--- a/InputData/elec/BRPSPTY/BAU RPS Percentage This Year.xlsx
+++ b/InputData/elec/BRPSPTY/BAU RPS Percentage This Year.xlsx
@@ -1,26 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri.sharepoint.com/sites/traccity/Shared Documents/HK 2050 is now/InputData FOR HONG KONG/UPDATE InputData for Hong Kong/InputData/elec/BRPSPTY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiyang.zhang\Desktop\eps-us-3.4.7 working_0117_wing_endofday\eps-us-3.4.7 HK working\InputData\elec\BRPSPTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04D77FA4-095E-40B7-8BA6-F99069F2AC0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E42B64-4BA7-4E70-837D-88659BC00F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27870" windowHeight="12810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BRPSPTY" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -28,25 +37,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>Sources:</t>
-  </si>
-  <si>
-    <t>Note:</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>RPS Fraction</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
   <si>
     <t>BRPSPTY BAU Renewable Portfolio Std Percentage This Year</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://re.emsd.gov.hk/english/gen/overview/over_re.html</t>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>Major resources of renewable energy in HK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>HK RE Net</t>
@@ -56,61 +57,309 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.enb.gov.hk/sites/default/files/pdf/ClimateActionPlanEng.pdf</t>
-  </si>
-  <si>
-    <t>Hong Kong's Climate Action Plan 2030+</t>
+    <t>https://re.emsd.gov.hk/english/gen/overview/over_re.html</t>
+  </si>
+  <si>
+    <t>Renewable energy potential and prediction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Environmental Bureau of Hong Kong </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>Hong Kong's Climate Action Plan 2030+</t>
+  </si>
+  <si>
+    <t>https://www.enb.gov.hk/sites/default/files/pdf/ClimateActionPlanEng.pdf</t>
+  </si>
+  <si>
     <t>Page 24, Figure 7</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>There is no specific policy of renewable energy percentage.</t>
+    <t>Total energy consumption in HK,2023</t>
+  </si>
+  <si>
+    <t>Hong Kong Energy Statistics</t>
+  </si>
+  <si>
+    <t>https://www.emsd.gov.hk/filemanager/en/content_762/HKEEUD2023.pdf</t>
+  </si>
+  <si>
+    <t>279907TJ</t>
+  </si>
+  <si>
+    <t>Share of wind, solar, waste(biomass) energy in HK</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HK EMSD </t>
+  </si>
+  <si>
+    <t>Chart 22</t>
+  </si>
+  <si>
+    <t>Note:</t>
   </si>
   <si>
     <t xml:space="preserve">According to Hong Kong renewable net, solar, wind and waste-to-energy are 3 major resources of renewable energy in Hong Kong. </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Major resources of renewable energy in HK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Renewable energy potential and prediction</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Total energy consumption in HK,2015</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hong Kong Energy Statistics</t>
-  </si>
-  <si>
-    <t>Page 6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Share of wind, solar, waste(biomass) energy in HK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>International energy agency</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.statistics.gov.hk/pub/B11000022015AN15B0100.pdf</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.iea.org/statistics/?country=HONGKONG&amp;year=2016&amp;category=Renewables&amp;indicator=WasteGenBySource&amp;mode=chart&amp;dataTable=RENEWABLES</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>CAP2050 sets the following goals: (1) 7.5%-10% RE by 2035 (2) 15% RE by 2050</t>
+  </si>
+  <si>
+    <t>RPS Fraction</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>Year2020</t>
+  </si>
+  <si>
+    <t>Year2021</t>
+  </si>
+  <si>
+    <t>Year2022</t>
+  </si>
+  <si>
+    <t>Year2023</t>
+  </si>
+  <si>
+    <t>Year2024</t>
+  </si>
+  <si>
+    <t>Year2025</t>
+  </si>
+  <si>
+    <t>Year2026</t>
+  </si>
+  <si>
+    <t>Year2027</t>
+  </si>
+  <si>
+    <t>Year2028</t>
+  </si>
+  <si>
+    <t>Year2029</t>
+  </si>
+  <si>
+    <t>Year2030</t>
+  </si>
+  <si>
+    <t>Year2031</t>
+  </si>
+  <si>
+    <t>Year2032</t>
+  </si>
+  <si>
+    <t>Year2033</t>
+  </si>
+  <si>
+    <t>Year2034</t>
+  </si>
+  <si>
+    <t>Year2035</t>
+  </si>
+  <si>
+    <t>Year2036</t>
+  </si>
+  <si>
+    <t>Year2037</t>
+  </si>
+  <si>
+    <t>Year2038</t>
+  </si>
+  <si>
+    <t>Year2039</t>
+  </si>
+  <si>
+    <t>Year2040</t>
+  </si>
+  <si>
+    <t>Year2041</t>
+  </si>
+  <si>
+    <t>Year2042</t>
+  </si>
+  <si>
+    <t>Year2043</t>
+  </si>
+  <si>
+    <t>Year2044</t>
+  </si>
+  <si>
+    <t>Year2045</t>
+  </si>
+  <si>
+    <t>Year2046</t>
+  </si>
+  <si>
+    <t>Year2047</t>
+  </si>
+  <si>
+    <t>Year2048</t>
+  </si>
+  <si>
+    <t>Year2049</t>
+  </si>
+  <si>
+    <t>Year2050</t>
+  </si>
+  <si>
+    <t>Year2051</t>
+  </si>
+  <si>
+    <t>Year2052</t>
+  </si>
+  <si>
+    <t>Year2053</t>
+  </si>
+  <si>
+    <t>Year2054</t>
+  </si>
+  <si>
+    <t>Year2055</t>
+  </si>
+  <si>
+    <t>Year2056</t>
+  </si>
+  <si>
+    <t>Year2057</t>
+  </si>
+  <si>
+    <t>Year2058</t>
+  </si>
+  <si>
+    <t>Year2059</t>
+  </si>
+  <si>
+    <t>Year2060</t>
+  </si>
+  <si>
+    <t>Year2061</t>
+  </si>
+  <si>
+    <t>Year2062</t>
+  </si>
+  <si>
+    <t>Year2063</t>
+  </si>
+  <si>
+    <t>Year2064</t>
+  </si>
+  <si>
+    <t>Year2065</t>
+  </si>
+  <si>
+    <t>Year2066</t>
+  </si>
+  <si>
+    <t>Year2067</t>
+  </si>
+  <si>
+    <t>Year2068</t>
+  </si>
+  <si>
+    <t>Year2069</t>
+  </si>
+  <si>
+    <t>Year2070</t>
+  </si>
+  <si>
+    <t>Year2071</t>
+  </si>
+  <si>
+    <t>Year2072</t>
+  </si>
+  <si>
+    <t>Year2073</t>
+  </si>
+  <si>
+    <t>Year2074</t>
+  </si>
+  <si>
+    <t>Year2075</t>
+  </si>
+  <si>
+    <t>Year2076</t>
+  </si>
+  <si>
+    <t>Year2077</t>
+  </si>
+  <si>
+    <t>Year2078</t>
+  </si>
+  <si>
+    <t>Year2079</t>
+  </si>
+  <si>
+    <t>Year2080</t>
+  </si>
+  <si>
+    <t>Year2081</t>
+  </si>
+  <si>
+    <t>Year2082</t>
+  </si>
+  <si>
+    <t>Year2083</t>
+  </si>
+  <si>
+    <t>Year2084</t>
+  </si>
+  <si>
+    <t>Year2085</t>
+  </si>
+  <si>
+    <t>Year2086</t>
+  </si>
+  <si>
+    <t>Year2087</t>
+  </si>
+  <si>
+    <t>Year2088</t>
+  </si>
+  <si>
+    <t>Year2089</t>
+  </si>
+  <si>
+    <t>Year2090</t>
+  </si>
+  <si>
+    <t>Year2091</t>
+  </si>
+  <si>
+    <t>Year2092</t>
+  </si>
+  <si>
+    <t>Year2093</t>
+  </si>
+  <si>
+    <t>Year2094</t>
+  </si>
+  <si>
+    <t>Year2095</t>
+  </si>
+  <si>
+    <t>Year2096</t>
+  </si>
+  <si>
+    <t>Year2097</t>
+  </si>
+  <si>
+    <t>Year2098</t>
+  </si>
+  <si>
+    <t>Year2099</t>
+  </si>
+  <si>
+    <t>Year2100</t>
+  </si>
+  <si>
+    <t>Note that this variable is populating the Future Year subscript.  It is not a normal time-series data variable.  Therefore, this sheet must include a value for every year that exists in the Future Year subscript (and no other years should be present).</t>
   </si>
 </sst>
 </file>
@@ -184,7 +433,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -202,6 +451,7 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -222,9 +472,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -262,9 +512,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -297,26 +547,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -349,26 +582,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -543,53 +759,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="122.7109375" customWidth="1"/>
+    <col min="2" max="2" width="122.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" s="2">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="B7" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -599,78 +815,80 @@
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="9" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="B12" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" s="5">
-        <v>2015</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="B17" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="B18" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="B19" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="B20" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="B21" s="5">
-        <v>2015</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="B22" s="6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="B23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="B25" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -681,9 +899,11 @@
   <hyperlinks>
     <hyperlink ref="B17" r:id="rId1" xr:uid="{F540E84A-1D6C-4701-8245-CCD10F2FCA98}"/>
     <hyperlink ref="B22" r:id="rId2" xr:uid="{507758C9-C9BE-4809-83CA-D05166759E9F}"/>
+    <hyperlink ref="B7" r:id="rId3" xr:uid="{6589F88B-8AE9-46AD-9807-DA21F3A36DA6}"/>
+    <hyperlink ref="B12" r:id="rId4" xr:uid="{2BD12A28-8F53-402D-AF9C-D8610CF4E378}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -692,128 +912,263 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:CD4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:82">
       <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1">
-        <v>2015</v>
-      </c>
-      <c r="C1">
-        <v>2016</v>
-      </c>
-      <c r="D1">
-        <v>2017</v>
-      </c>
-      <c r="E1">
-        <v>2018</v>
-      </c>
-      <c r="F1">
-        <v>2019</v>
-      </c>
-      <c r="G1">
-        <v>2020</v>
-      </c>
-      <c r="H1">
-        <v>2021</v>
-      </c>
-      <c r="I1">
-        <v>2022</v>
-      </c>
-      <c r="J1">
-        <v>2023</v>
-      </c>
-      <c r="K1">
-        <v>2024</v>
-      </c>
-      <c r="L1">
-        <v>2025</v>
-      </c>
-      <c r="M1">
-        <v>2026</v>
-      </c>
-      <c r="N1">
-        <v>2027</v>
-      </c>
-      <c r="O1">
-        <v>2028</v>
-      </c>
-      <c r="P1">
-        <v>2029</v>
-      </c>
-      <c r="Q1">
-        <v>2030</v>
-      </c>
-      <c r="R1">
-        <v>2031</v>
-      </c>
-      <c r="S1">
-        <v>2032</v>
-      </c>
-      <c r="T1">
-        <v>2033</v>
-      </c>
-      <c r="U1">
-        <v>2034</v>
-      </c>
-      <c r="V1">
-        <v>2035</v>
-      </c>
-      <c r="W1">
-        <v>2036</v>
-      </c>
-      <c r="X1">
-        <v>2037</v>
-      </c>
-      <c r="Y1">
-        <v>2038</v>
-      </c>
-      <c r="Z1">
-        <v>2039</v>
-      </c>
-      <c r="AA1">
-        <v>2040</v>
-      </c>
-      <c r="AB1">
-        <v>2041</v>
-      </c>
-      <c r="AC1">
-        <v>2042</v>
-      </c>
-      <c r="AD1">
-        <v>2043</v>
-      </c>
-      <c r="AE1">
-        <v>2044</v>
-      </c>
-      <c r="AF1">
-        <v>2045</v>
-      </c>
-      <c r="AG1">
-        <v>2046</v>
-      </c>
-      <c r="AH1">
-        <v>2047</v>
-      </c>
-      <c r="AI1">
-        <v>2048</v>
-      </c>
-      <c r="AJ1">
-        <v>2049</v>
-      </c>
-      <c r="AK1">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" s="7" customFormat="1">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>77</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>78</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>80</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>81</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>84</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>85</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>86</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>95</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:82" s="7" customFormat="1">
       <c r="A2" s="7" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B2" s="8">
         <v>0</v>
@@ -876,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="8">
-        <v>0</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="W2" s="8">
         <v>0</v>
@@ -921,7 +1276,147 @@
         <v>0</v>
       </c>
       <c r="AK2" s="8">
-        <v>0</v>
+        <v>0.15</v>
+      </c>
+      <c r="AL2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BT2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BU2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BV2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BW2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BX2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BY2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BZ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="CA2" s="8">
+        <v>0</v>
+      </c>
+      <c r="CB2" s="8">
+        <v>0</v>
+      </c>
+      <c r="CC2" s="8">
+        <v>0</v>
+      </c>
+      <c r="CD2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:82">
+      <c r="A4" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -931,31 +1426,52 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb176f07-3112-4ee9-93fd-ae2cb5f3e433">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b15a3a4-8173-42d6-9deb-398ec38eca4b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -963,24 +1479,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -999,70 +1576,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1164,50 +1694,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80920222-64DA-4CE1-B8EC-C252475073B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C70947-0330-4C93-BD6E-06A78B1BD079}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D05ACA9-20B8-4CDE-B9B1-04F0B4C8A025}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C70947-0330-4C93-BD6E-06A78B1BD079}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{050BAF0C-2B0A-405C-B60A-C8F0E7DAC282}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>